--- a/Planificacion/Gantt Chart Cronograma.xlsx
+++ b/Planificacion/Gantt Chart Cronograma.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/13b979beda9c5651/Documentos/UASD/Semestre 2026-10/Progamacion 3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rayke\Documents\Programacion Web\Programacion 3\Proyecto Final\Reto-3-Grupo-J\Planificacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{10377103-9268-42CD-B802-50DE7F974AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3E080B5-14EF-4676-B6F8-03ED33CA5E86}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF59A3B-31EB-4F17-B043-86D8907DB8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="7650" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,90 +44,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Raykel Villar</author>
-  </authors>
-  <commentList>
-    <comment ref="B31" authorId="0" shapeId="0" xr:uid="{CB5F8FE0-3A07-4DD7-9A6A-C9EB65374E0F}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Raykel Villar:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Modificar Productos, Agregar nuevos, deshabilitar productos. Cambiar Roles.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B32" authorId="0" shapeId="0" xr:uid="{A3221A40-20FC-434F-8F6B-632DA2F27663}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Raykel Villar:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Modificar Productos, Agregar nuevos, deshabilitar productos. Cambiar Roles.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B33" authorId="0" shapeId="0" xr:uid="{AB31A21F-8F32-4341-99B6-39E3A43DB709}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Raykel Villar:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Modificar Productos, Agregar nuevos, deshabilitar productos. Cambiar Roles.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="45">
   <si>
     <t xml:space="preserve">Do not delete this row. This row is hidden to preserve a formula that is used to highlight the current day within the project schedule. </t>
   </si>
@@ -195,79 +113,73 @@
     <t>B. Estructura de Desglose del Trabajo (EDT / WBS)</t>
   </si>
   <si>
-    <t>Reunion Virtual Google Meets</t>
-  </si>
-  <si>
-    <t>Paginas Login y Registro HTML</t>
-  </si>
-  <si>
-    <t>Paginas Login y Registro CSS</t>
-  </si>
-  <si>
-    <t>Paginas Login y Registro Backend</t>
-  </si>
-  <si>
     <t>Crear Roles Backend</t>
   </si>
   <si>
-    <t>Base Datos</t>
-  </si>
-  <si>
-    <t>Pagina De Inicio HTML</t>
-  </si>
-  <si>
-    <t>Pagina De Inicio CSS</t>
-  </si>
-  <si>
-    <t>Pagina De Inicio Backend</t>
-  </si>
-  <si>
-    <t>Pagina Lista de Favoritos HTML</t>
-  </si>
-  <si>
-    <t>Pagina Lista de Favoritos CSS</t>
-  </si>
-  <si>
-    <t>Pagina Lista de Favoritos Backend</t>
-  </si>
-  <si>
-    <t>Pagina Administrador HTML</t>
-  </si>
-  <si>
-    <t>Pagina Administrador CSS</t>
-  </si>
-  <si>
-    <t>Pagina Administrador Backend</t>
-  </si>
-  <si>
     <t>Crear React App</t>
   </si>
   <si>
-    <t>Pagina Ordenes HTML</t>
-  </si>
-  <si>
-    <t>Pagina Ordenes CSS</t>
-  </si>
-  <si>
-    <t>Pagina Ordenes Backend</t>
-  </si>
-  <si>
-    <t>Pagina Articulos HTML</t>
-  </si>
-  <si>
-    <t>Pagina Articulos CSS</t>
-  </si>
-  <si>
-    <t>Pagina Articulos Backend</t>
-  </si>
-  <si>
-    <t>Pagina De Departamentos HTML (Opcional)</t>
-  </si>
-  <si>
-    <t>Pagina De Departamentos CSS (Optional)</t>
-  </si>
-  <si>
-    <t>Pagina De Departamentos Backend (Optional)</t>
+    <t>Paginas Login y Registro</t>
+  </si>
+  <si>
+    <t>Pagina Productos</t>
+  </si>
+  <si>
+    <t>Header</t>
+  </si>
+  <si>
+    <t>Footer</t>
+  </si>
+  <si>
+    <t>Pagina Suplidores</t>
+  </si>
+  <si>
+    <t>Pagina De Inicio</t>
+  </si>
+  <si>
+    <t>Pagina Servicio Al Cliente</t>
+  </si>
+  <si>
+    <t>Pagina Inicio Admin</t>
+  </si>
+  <si>
+    <t>Pagina Lista De Favoritos</t>
+  </si>
+  <si>
+    <t>Pagina Carrito</t>
+  </si>
+  <si>
+    <t>Pagina Ordenes Admin</t>
+  </si>
+  <si>
+    <t>Pagina Ordenes</t>
+  </si>
+  <si>
+    <t>Pagina Productos Admin</t>
+  </si>
+  <si>
+    <t>Pagina Movimientos De Inventario</t>
+  </si>
+  <si>
+    <t>Base De Datos</t>
+  </si>
+  <si>
+    <t>Pagina Suplidores Admin</t>
+  </si>
+  <si>
+    <t>Crear Funciones Para Pagina Productos</t>
+  </si>
+  <si>
+    <t>Crear Funciones Para Pagina Suplidores</t>
+  </si>
+  <si>
+    <t>Crear Funciones Para Pagina Login y Registro</t>
+  </si>
+  <si>
+    <t>Reunion Virtual Google Meets 1</t>
+  </si>
+  <si>
+    <t>Reunion Virtual Google Meets 2</t>
   </si>
 </sst>
 </file>
@@ -281,7 +193,7 @@
     <numFmt numFmtId="166" formatCode="mmm\ d\,\ yyyy"/>
     <numFmt numFmtId="167" formatCode="d"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -482,19 +394,6 @@
       <name val="Arial Black"/>
       <family val="2"/>
       <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1006,48 +905,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
       <extLst>
@@ -1056,6 +913,48 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="14" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Comma" xfId="4" builtinId="3" customBuiltin="1"/>
@@ -1699,11 +1598,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC50"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.58203125" style="6" customWidth="1"/>
@@ -1727,28 +1626,28 @@
       <c r="E1" s="13"/>
       <c r="F1" s="14"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="83" t="s">
+      <c r="I1" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="84"/>
-      <c r="O1" s="84"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
       <c r="P1" s="17"/>
-      <c r="Q1" s="81">
+      <c r="Q1" s="82">
         <v>46130</v>
       </c>
-      <c r="R1" s="82"/>
-      <c r="S1" s="82"/>
-      <c r="T1" s="82"/>
-      <c r="U1" s="82"/>
-      <c r="V1" s="82"/>
-      <c r="W1" s="82"/>
-      <c r="X1" s="82"/>
-      <c r="Y1" s="82"/>
-      <c r="Z1" s="82"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="83"/>
+      <c r="T1" s="83"/>
+      <c r="U1" s="83"/>
+      <c r="V1" s="83"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="83"/>
+      <c r="Z1" s="83"/>
     </row>
     <row r="2" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B2" s="68" t="s">
@@ -1758,28 +1657,28 @@
       <c r="D2" s="15"/>
       <c r="E2" s="16"/>
       <c r="F2" s="15"/>
-      <c r="I2" s="85" t="s">
+      <c r="I2" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="86"/>
-      <c r="K2" s="86"/>
-      <c r="L2" s="86"/>
-      <c r="M2" s="86"/>
-      <c r="N2" s="86"/>
-      <c r="O2" s="86"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
       <c r="P2" s="67"/>
-      <c r="Q2" s="79">
+      <c r="Q2" s="90">
         <v>2</v>
       </c>
-      <c r="R2" s="80"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="80"/>
-      <c r="U2" s="80"/>
-      <c r="V2" s="80"/>
-      <c r="W2" s="80"/>
-      <c r="X2" s="80"/>
-      <c r="Y2" s="80"/>
-      <c r="Z2" s="80"/>
+      <c r="R2" s="91"/>
+      <c r="S2" s="91"/>
+      <c r="T2" s="91"/>
+      <c r="U2" s="91"/>
+      <c r="V2" s="91"/>
+      <c r="W2" s="91"/>
+      <c r="X2" s="91"/>
+      <c r="Y2" s="91"/>
+      <c r="Z2" s="91"/>
     </row>
     <row r="3" spans="1:29" s="18" customFormat="1" ht="44.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
@@ -1788,27 +1687,27 @@
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="20"/>
-      <c r="I3" s="83" t="s">
+      <c r="I3" s="84" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="84"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="84"/>
-      <c r="M3" s="84"/>
-      <c r="N3" s="84"/>
-      <c r="O3" s="84"/>
-      <c r="Q3" s="81">
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="85"/>
+      <c r="Q3" s="82">
         <v>46150</v>
       </c>
-      <c r="R3" s="82"/>
-      <c r="S3" s="82"/>
-      <c r="T3" s="82"/>
-      <c r="U3" s="82"/>
-      <c r="V3" s="82"/>
-      <c r="W3" s="82"/>
-      <c r="X3" s="82"/>
-      <c r="Y3" s="82"/>
-      <c r="Z3" s="82"/>
+      <c r="R3" s="83"/>
+      <c r="S3" s="83"/>
+      <c r="T3" s="83"/>
+      <c r="U3" s="83"/>
+      <c r="V3" s="83"/>
+      <c r="W3" s="83"/>
+      <c r="X3" s="83"/>
+      <c r="Y3" s="83"/>
+      <c r="Z3" s="83"/>
     </row>
     <row r="4" spans="1:29" s="18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
@@ -1830,52 +1729,52 @@
       <c r="A6" s="7"/>
       <c r="B6" s="21"/>
       <c r="E6" s="22"/>
-      <c r="I6" s="75">
+      <c r="I6" s="88">
         <f>I7</f>
         <v>46130</v>
       </c>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="76"/>
-      <c r="N6" s="76"/>
-      <c r="O6" s="76"/>
-      <c r="P6" s="76">
+      <c r="J6" s="89"/>
+      <c r="K6" s="89"/>
+      <c r="L6" s="89"/>
+      <c r="M6" s="89"/>
+      <c r="N6" s="89"/>
+      <c r="O6" s="89"/>
+      <c r="P6" s="89">
         <f>P7</f>
         <v>46137</v>
       </c>
-      <c r="Q6" s="76"/>
-      <c r="R6" s="76"/>
-      <c r="S6" s="76"/>
-      <c r="T6" s="76"/>
-      <c r="U6" s="76"/>
-      <c r="V6" s="76"/>
-      <c r="W6" s="76">
+      <c r="Q6" s="89"/>
+      <c r="R6" s="89"/>
+      <c r="S6" s="89"/>
+      <c r="T6" s="89"/>
+      <c r="U6" s="89"/>
+      <c r="V6" s="89"/>
+      <c r="W6" s="89">
         <f>W7</f>
         <v>46144</v>
       </c>
-      <c r="X6" s="76"/>
-      <c r="Y6" s="76"/>
-      <c r="Z6" s="76"/>
-      <c r="AA6" s="76"/>
-      <c r="AB6" s="76"/>
-      <c r="AC6" s="76"/>
+      <c r="X6" s="89"/>
+      <c r="Y6" s="89"/>
+      <c r="Z6" s="89"/>
+      <c r="AA6" s="89"/>
+      <c r="AB6" s="89"/>
+      <c r="AC6" s="89"/>
     </row>
     <row r="7" spans="1:29" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="87"/>
-      <c r="B7" s="88" t="s">
+      <c r="A7" s="76"/>
+      <c r="B7" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="90" t="s">
+      <c r="C7" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="77" t="s">
+      <c r="D7" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="77" t="s">
+      <c r="E7" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="77" t="s">
+      <c r="F7" s="81" t="s">
         <v>6</v>
       </c>
       <c r="I7" s="23">
@@ -1964,12 +1863,12 @@
       </c>
     </row>
     <row r="8" spans="1:29" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="87"/>
-      <c r="B8" s="89"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="78"/>
-      <c r="E8" s="78"/>
-      <c r="F8" s="78"/>
+      <c r="A8" s="76"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="80"/>
       <c r="I8" s="26" t="str">
         <f t="shared" ref="I8:AC8" si="1">LEFT(TEXT(I7,"ddd"),1)</f>
         <v>S</v>
@@ -2101,7 +2000,7 @@
       <c r="F10" s="35"/>
       <c r="G10" s="10"/>
       <c r="H10" s="5" t="str">
-        <f t="shared" ref="H10:H47" si="2">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <f t="shared" ref="H10:H48" si="2">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
       <c r="I10" s="36"/>
@@ -2127,7 +2026,7 @@
       <c r="AC10" s="36"/>
     </row>
     <row r="11" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="91" t="b">
+      <c r="A11" s="75" t="b">
         <v>1</v>
       </c>
       <c r="B11" s="38" t="s">
@@ -2174,7 +2073,7 @@
       <c r="AC11" s="41"/>
     </row>
     <row r="12" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="91" t="b">
+      <c r="A12" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B12" s="42" t="s">
@@ -2184,7 +2083,7 @@
         <v>13</v>
       </c>
       <c r="D12" s="43">
-        <f t="shared" ref="D12:D17" si="3">IF(A12, 100%, 0%)</f>
+        <f t="shared" ref="D12:D42" si="3">IF(A12, 100%, 0%)</f>
         <v>0</v>
       </c>
       <c r="E12" s="44">
@@ -2221,8 +2120,8 @@
       <c r="AC12" s="41"/>
     </row>
     <row r="13" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="91" t="b">
-        <v>0</v>
+      <c r="A13" s="75" t="b">
+        <v>1</v>
       </c>
       <c r="B13" s="42" t="s">
         <v>18</v>
@@ -2230,16 +2129,20 @@
       <c r="C13" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="43">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
+      <c r="D13" s="39">
+        <f>IF(A13, 100%, 0%)</f>
+        <v>1</v>
+      </c>
+      <c r="E13" s="44">
+        <v>46134</v>
+      </c>
+      <c r="F13" s="44">
+        <v>46134</v>
+      </c>
       <c r="G13" s="10"/>
-      <c r="H13" s="5" t="str">
+      <c r="H13" s="5">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I13" s="41"/>
       <c r="J13" s="41"/>
@@ -2264,7 +2167,7 @@
       <c r="AC13" s="41"/>
     </row>
     <row r="14" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="91" t="b">
+      <c r="A14" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B14" s="42" t="s">
@@ -2309,7 +2212,7 @@
       <c r="AC14" s="41"/>
     </row>
     <row r="15" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="91" t="b">
+      <c r="A15" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B15" s="42" t="s">
@@ -2354,11 +2257,11 @@
       <c r="AC15" s="41"/>
     </row>
     <row r="16" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="91" t="b">
+      <c r="A16" s="75" t="b">
         <v>1</v>
       </c>
       <c r="B16" s="69" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C16" s="74" t="s">
         <v>19</v>
@@ -2398,24 +2301,24 @@
       <c r="AC16" s="41"/>
     </row>
     <row r="17" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="91" t="b">
+      <c r="A17" s="75" t="b">
         <v>1</v>
       </c>
       <c r="B17" s="69" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C17" s="74" t="s">
         <v>19</v>
       </c>
       <c r="D17" s="70">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D17" si="4">IF(A17, 100%, 0%)</f>
         <v>1</v>
       </c>
       <c r="E17" s="71">
-        <v>46137</v>
+        <v>46141</v>
       </c>
       <c r="F17" s="71">
-        <v>46137</v>
+        <v>46141</v>
       </c>
       <c r="G17" s="10"/>
       <c r="H17" s="5"/>
@@ -2442,66 +2345,66 @@
       <c r="AC17" s="41"/>
     </row>
     <row r="18" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="7"/>
-      <c r="B18" s="46" t="s">
+      <c r="A18" s="75" t="b">
+        <v>1</v>
+      </c>
+      <c r="B18" s="69" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="70">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="E18" s="71">
+        <v>46137</v>
+      </c>
+      <c r="F18" s="71">
+        <v>46137</v>
+      </c>
+      <c r="G18" s="10"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="41"/>
+      <c r="P18" s="41"/>
+      <c r="Q18" s="41"/>
+      <c r="R18" s="41"/>
+      <c r="S18" s="41"/>
+      <c r="T18" s="41"/>
+      <c r="U18" s="41"/>
+      <c r="V18" s="41"/>
+      <c r="W18" s="41"/>
+      <c r="X18" s="41"/>
+      <c r="Y18" s="41"/>
+      <c r="Z18" s="41"/>
+      <c r="AA18" s="41"/>
+      <c r="AB18" s="41"/>
+      <c r="AC18" s="41"/>
+    </row>
+    <row r="19" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="7"/>
+      <c r="B19" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="47"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="5" t="str">
+      <c r="C19" s="47"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="5" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="91" t="b">
-        <v>0</v>
-      </c>
-      <c r="B19" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="52" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="53"/>
-      <c r="E19" s="54">
-        <v>46137</v>
-      </c>
-      <c r="F19" s="54">
-        <v>46143</v>
-      </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="5">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="41"/>
-      <c r="M19" s="41"/>
-      <c r="N19" s="41"/>
-      <c r="O19" s="41"/>
-      <c r="P19" s="41"/>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="41"/>
-      <c r="S19" s="41"/>
-      <c r="T19" s="41"/>
-      <c r="U19" s="41"/>
-      <c r="V19" s="41"/>
-      <c r="W19" s="41"/>
-      <c r="X19" s="41"/>
-      <c r="Y19" s="41"/>
-      <c r="Z19" s="41"/>
-      <c r="AA19" s="41"/>
-      <c r="AB19" s="41"/>
-      <c r="AC19" s="41"/>
-    </row>
     <row r="20" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="91" t="b">
+      <c r="A20" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B20" s="51" t="s">
@@ -2510,17 +2413,20 @@
       <c r="C20" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="53"/>
+      <c r="D20" s="53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E20" s="54">
-        <v>46137</v>
+        <v>46141</v>
       </c>
       <c r="F20" s="54">
-        <v>46143</v>
+        <v>46142</v>
       </c>
       <c r="G20" s="10"/>
       <c r="H20" s="5">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I20" s="41"/>
       <c r="J20" s="41"/>
@@ -2534,8 +2440,8 @@
       <c r="R20" s="41"/>
       <c r="S20" s="41"/>
       <c r="T20" s="41"/>
-      <c r="U20" s="45"/>
-      <c r="V20" s="45"/>
+      <c r="U20" s="41"/>
+      <c r="V20" s="41"/>
       <c r="W20" s="41"/>
       <c r="X20" s="41"/>
       <c r="Y20" s="41"/>
@@ -2545,26 +2451,29 @@
       <c r="AC20" s="41"/>
     </row>
     <row r="21" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="91" t="b">
+      <c r="A21" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B21" s="51" t="s">
         <v>25</v>
       </c>
       <c r="C21" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="53"/>
+        <v>15</v>
+      </c>
+      <c r="D21" s="53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E21" s="54">
-        <v>46137</v>
+        <v>46139</v>
       </c>
       <c r="F21" s="54">
-        <v>46143</v>
+        <v>46140</v>
       </c>
       <c r="G21" s="10"/>
       <c r="H21" s="5">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I21" s="41"/>
       <c r="J21" s="41"/>
@@ -2578,8 +2487,8 @@
       <c r="R21" s="41"/>
       <c r="S21" s="41"/>
       <c r="T21" s="41"/>
-      <c r="U21" s="41"/>
-      <c r="V21" s="41"/>
+      <c r="U21" s="45"/>
+      <c r="V21" s="45"/>
       <c r="W21" s="41"/>
       <c r="X21" s="41"/>
       <c r="Y21" s="41"/>
@@ -2589,24 +2498,30 @@
       <c r="AC21" s="41"/>
     </row>
     <row r="22" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="91" t="b">
+      <c r="A22" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C22" s="52" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="53"/>
+        <v>14</v>
+      </c>
+      <c r="D22" s="53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E22" s="54">
-        <v>46137</v>
+        <v>46142</v>
       </c>
       <c r="F22" s="54">
         <v>46143</v>
       </c>
       <c r="G22" s="10"/>
-      <c r="H22" s="5"/>
+      <c r="H22" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
       <c r="I22" s="41"/>
       <c r="J22" s="41"/>
       <c r="K22" s="41"/>
@@ -2630,18 +2545,21 @@
       <c r="AC22" s="41"/>
     </row>
     <row r="23" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="91" t="b">
+      <c r="A23" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B23" s="51" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C23" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="53"/>
+      <c r="D23" s="53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E23" s="54">
-        <v>46137</v>
+        <v>46142</v>
       </c>
       <c r="F23" s="54">
         <v>46143</v>
@@ -2671,21 +2589,24 @@
       <c r="AC23" s="41"/>
     </row>
     <row r="24" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="91" t="b">
+      <c r="A24" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B24" s="51" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C24" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="53"/>
+        <v>15</v>
+      </c>
+      <c r="D24" s="53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E24" s="54">
-        <v>46137</v>
+        <v>46139</v>
       </c>
       <c r="F24" s="54">
-        <v>46143</v>
+        <v>46142</v>
       </c>
       <c r="G24" s="10"/>
       <c r="H24" s="5"/>
@@ -2712,21 +2633,24 @@
       <c r="AC24" s="41"/>
     </row>
     <row r="25" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="91" t="b">
+      <c r="A25" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C25" s="52" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="53"/>
+        <v>14</v>
+      </c>
+      <c r="D25" s="53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E25" s="54">
-        <v>46137</v>
+        <v>46140</v>
       </c>
       <c r="F25" s="54">
-        <v>46143</v>
+        <v>46141</v>
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="5"/>
@@ -2753,21 +2677,24 @@
       <c r="AC25" s="41"/>
     </row>
     <row r="26" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="91" t="b">
+      <c r="A26" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C26" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="D26" s="53"/>
+      <c r="D26" s="53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E26" s="54">
-        <v>46137</v>
+        <v>46140</v>
       </c>
       <c r="F26" s="54">
-        <v>46143</v>
+        <v>46141</v>
       </c>
       <c r="G26" s="10"/>
       <c r="H26" s="5"/>
@@ -2794,18 +2721,21 @@
       <c r="AC26" s="41"/>
     </row>
     <row r="27" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="91" t="b">
+      <c r="A27" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C27" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="D27" s="53"/>
+      <c r="D27" s="53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E27" s="54">
-        <v>46137</v>
+        <v>46142</v>
       </c>
       <c r="F27" s="54">
         <v>46143</v>
@@ -2835,21 +2765,24 @@
       <c r="AC27" s="41"/>
     </row>
     <row r="28" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="91" t="b">
+      <c r="A28" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C28" s="52" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="53"/>
+        <v>13</v>
+      </c>
+      <c r="D28" s="53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E28" s="54">
-        <v>46137</v>
+        <v>46139</v>
       </c>
       <c r="F28" s="54">
-        <v>46143</v>
+        <v>46141</v>
       </c>
       <c r="G28" s="10"/>
       <c r="H28" s="5"/>
@@ -2876,18 +2809,21 @@
       <c r="AC28" s="41"/>
     </row>
     <row r="29" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="91" t="b">
+      <c r="A29" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B29" s="51" t="s">
         <v>32</v>
       </c>
       <c r="C29" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="53"/>
+        <v>15</v>
+      </c>
+      <c r="D29" s="53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E29" s="54">
-        <v>46137</v>
+        <v>46141</v>
       </c>
       <c r="F29" s="54">
         <v>46143</v>
@@ -2917,18 +2853,21 @@
       <c r="AC29" s="41"/>
     </row>
     <row r="30" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="91" t="b">
+      <c r="A30" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B30" s="51" t="s">
         <v>33</v>
       </c>
       <c r="C30" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="53"/>
+        <v>14</v>
+      </c>
+      <c r="D30" s="53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E30" s="54">
-        <v>46137</v>
+        <v>46141</v>
       </c>
       <c r="F30" s="54">
         <v>46143</v>
@@ -2958,18 +2897,21 @@
       <c r="AC30" s="41"/>
     </row>
     <row r="31" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="91" t="b">
+      <c r="A31" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B31" s="51" t="s">
         <v>34</v>
       </c>
       <c r="C31" s="52" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="53"/>
+        <v>13</v>
+      </c>
+      <c r="D31" s="53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E31" s="54">
-        <v>46137</v>
+        <v>46141</v>
       </c>
       <c r="F31" s="54">
         <v>46143</v>
@@ -2999,21 +2941,24 @@
       <c r="AC31" s="41"/>
     </row>
     <row r="32" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="91" t="b">
+      <c r="A32" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B32" s="51" t="s">
         <v>35</v>
       </c>
       <c r="C32" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32" s="53"/>
+        <v>15</v>
+      </c>
+      <c r="D32" s="53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E32" s="54">
-        <v>46137</v>
+        <v>46140</v>
       </c>
       <c r="F32" s="54">
-        <v>46143</v>
+        <v>46141</v>
       </c>
       <c r="G32" s="10"/>
       <c r="H32" s="5"/>
@@ -3040,7 +2985,7 @@
       <c r="AC32" s="41"/>
     </row>
     <row r="33" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="91" t="b">
+      <c r="A33" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B33" s="51" t="s">
@@ -3049,12 +2994,15 @@
       <c r="C33" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="53"/>
+      <c r="D33" s="53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E33" s="54">
-        <v>46137</v>
+        <v>46139</v>
       </c>
       <c r="F33" s="54">
-        <v>46143</v>
+        <v>46140</v>
       </c>
       <c r="G33" s="10"/>
       <c r="H33" s="5"/>
@@ -3081,18 +3029,21 @@
       <c r="AC33" s="41"/>
     </row>
     <row r="34" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="91" t="b">
+      <c r="A34" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B34" s="51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C34" s="52" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="53"/>
+        <v>13</v>
+      </c>
+      <c r="D34" s="53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E34" s="54">
-        <v>46137</v>
+        <v>46141</v>
       </c>
       <c r="F34" s="54">
         <v>46143</v>
@@ -3122,21 +3073,24 @@
       <c r="AC34" s="41"/>
     </row>
     <row r="35" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="91" t="b">
-        <v>0</v>
+      <c r="A35" s="75" t="b">
+        <v>1</v>
       </c>
       <c r="B35" s="51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C35" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="D35" s="53"/>
+        <v>13</v>
+      </c>
+      <c r="D35" s="53">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
       <c r="E35" s="54">
         <v>46137</v>
       </c>
       <c r="F35" s="54">
-        <v>46143</v>
+        <v>46138</v>
       </c>
       <c r="G35" s="10"/>
       <c r="H35" s="5"/>
@@ -3163,21 +3117,24 @@
       <c r="AC35" s="41"/>
     </row>
     <row r="36" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="91" t="b">
+      <c r="A36" s="75" t="b">
         <v>0</v>
       </c>
       <c r="B36" s="51" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C36" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="53"/>
+        <v>15</v>
+      </c>
+      <c r="D36" s="53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E36" s="54">
         <v>46137</v>
       </c>
       <c r="F36" s="54">
-        <v>46143</v>
+        <v>46138</v>
       </c>
       <c r="G36" s="10"/>
       <c r="H36" s="5"/>
@@ -3204,21 +3161,24 @@
       <c r="AC36" s="41"/>
     </row>
     <row r="37" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="91" t="b">
-        <v>0</v>
+      <c r="A37" s="75" t="b">
+        <v>1</v>
       </c>
       <c r="B37" s="51" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="C37" s="52" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="53"/>
+        <v>13</v>
+      </c>
+      <c r="D37" s="53">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
       <c r="E37" s="54">
-        <v>46137</v>
+        <v>46139</v>
       </c>
       <c r="F37" s="54">
-        <v>46143</v>
+        <v>46139</v>
       </c>
       <c r="G37" s="10"/>
       <c r="H37" s="5"/>
@@ -3245,21 +3205,24 @@
       <c r="AC37" s="41"/>
     </row>
     <row r="38" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="91" t="b">
-        <v>0</v>
+      <c r="A38" s="75" t="b">
+        <v>1</v>
       </c>
       <c r="B38" s="51" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C38" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="D38" s="53"/>
+        <v>13</v>
+      </c>
+      <c r="D38" s="53">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
       <c r="E38" s="54">
-        <v>46137</v>
+        <v>46139</v>
       </c>
       <c r="F38" s="54">
-        <v>46143</v>
+        <v>46139</v>
       </c>
       <c r="G38" s="10"/>
       <c r="H38" s="5"/>
@@ -3286,21 +3249,24 @@
       <c r="AC38" s="41"/>
     </row>
     <row r="39" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="91" t="b">
-        <v>0</v>
+      <c r="A39" s="75" t="b">
+        <v>1</v>
       </c>
       <c r="B39" s="51" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C39" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="53"/>
+      <c r="D39" s="53">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
       <c r="E39" s="54">
-        <v>46137</v>
+        <v>46140</v>
       </c>
       <c r="F39" s="54">
-        <v>46143</v>
+        <v>46140</v>
       </c>
       <c r="G39" s="10"/>
       <c r="H39" s="5"/>
@@ -3327,27 +3293,27 @@
       <c r="AC39" s="41"/>
     </row>
     <row r="40" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="91" t="b">
-        <v>0</v>
+      <c r="A40" s="75" t="b">
+        <v>1</v>
       </c>
       <c r="B40" s="51" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C40" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="D40" s="53"/>
+      <c r="D40" s="53">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
       <c r="E40" s="54">
-        <v>46137</v>
+        <v>46140</v>
       </c>
       <c r="F40" s="54">
-        <v>46143</v>
+        <v>46140</v>
       </c>
       <c r="G40" s="10"/>
-      <c r="H40" s="5">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
+      <c r="H40" s="5"/>
       <c r="I40" s="41"/>
       <c r="J40" s="41"/>
       <c r="K40" s="41"/>
@@ -3364,23 +3330,22 @@
       <c r="V40" s="41"/>
       <c r="W40" s="41"/>
       <c r="X40" s="41"/>
-      <c r="Y40" s="45"/>
+      <c r="Y40" s="41"/>
       <c r="Z40" s="41"/>
       <c r="AA40" s="41"/>
       <c r="AB40" s="41"/>
       <c r="AC40" s="41"/>
     </row>
     <row r="41" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="91" t="b">
-        <v>0</v>
-      </c>
-      <c r="B41" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="C41" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" s="53"/>
+      <c r="A41" s="75" t="b">
+        <v>0</v>
+      </c>
+      <c r="B41" s="51"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="E41" s="54">
         <v>46137</v>
       </c>
@@ -3408,81 +3373,90 @@
       <c r="V41" s="41"/>
       <c r="W41" s="41"/>
       <c r="X41" s="41"/>
-      <c r="Y41" s="41"/>
+      <c r="Y41" s="45"/>
       <c r="Z41" s="41"/>
       <c r="AA41" s="41"/>
       <c r="AB41" s="41"/>
       <c r="AC41" s="41"/>
     </row>
     <row r="42" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="6"/>
-      <c r="B42" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="56"/>
-      <c r="D42" s="57"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="59"/>
+      <c r="A42" s="75" t="b">
+        <v>0</v>
+      </c>
+      <c r="B42" s="51"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="53">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E42" s="54">
+        <v>46137</v>
+      </c>
+      <c r="F42" s="54">
+        <v>46143</v>
+      </c>
       <c r="G42" s="10"/>
-      <c r="H42" s="5" t="str">
+      <c r="H42" s="5">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="I42" s="60"/>
-      <c r="J42" s="60"/>
-      <c r="K42" s="60"/>
-      <c r="L42" s="60"/>
-      <c r="M42" s="60"/>
-      <c r="N42" s="60"/>
-      <c r="O42" s="60"/>
-      <c r="P42" s="60"/>
-      <c r="Q42" s="60"/>
-      <c r="R42" s="60"/>
-      <c r="S42" s="60"/>
-      <c r="T42" s="60"/>
-      <c r="U42" s="60"/>
-      <c r="V42" s="60"/>
-      <c r="W42" s="60"/>
-      <c r="X42" s="60"/>
-      <c r="Y42" s="60"/>
-      <c r="Z42" s="60"/>
-      <c r="AA42" s="60"/>
-      <c r="AB42" s="60"/>
-      <c r="AC42" s="60"/>
+        <v>7</v>
+      </c>
+      <c r="I42" s="41"/>
+      <c r="J42" s="41"/>
+      <c r="K42" s="41"/>
+      <c r="L42" s="41"/>
+      <c r="M42" s="41"/>
+      <c r="N42" s="41"/>
+      <c r="O42" s="41"/>
+      <c r="P42" s="41"/>
+      <c r="Q42" s="41"/>
+      <c r="R42" s="41"/>
+      <c r="S42" s="41"/>
+      <c r="T42" s="41"/>
+      <c r="U42" s="41"/>
+      <c r="V42" s="41"/>
+      <c r="W42" s="41"/>
+      <c r="X42" s="41"/>
+      <c r="Y42" s="41"/>
+      <c r="Z42" s="41"/>
+      <c r="AA42" s="41"/>
+      <c r="AB42" s="41"/>
+      <c r="AC42" s="41"/>
     </row>
     <row r="43" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="6"/>
-      <c r="B43" s="61"/>
-      <c r="C43" s="62"/>
-      <c r="D43" s="63"/>
-      <c r="E43" s="64"/>
-      <c r="F43" s="64"/>
+      <c r="B43" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="56"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="58"/>
+      <c r="F43" s="59"/>
       <c r="G43" s="10"/>
       <c r="H43" s="5" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I43" s="41"/>
-      <c r="J43" s="41"/>
-      <c r="K43" s="41"/>
-      <c r="L43" s="41"/>
-      <c r="M43" s="41"/>
-      <c r="N43" s="41"/>
-      <c r="O43" s="41"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="41"/>
-      <c r="S43" s="41"/>
-      <c r="T43" s="41"/>
-      <c r="U43" s="41"/>
-      <c r="V43" s="41"/>
-      <c r="W43" s="41"/>
-      <c r="X43" s="41"/>
-      <c r="Y43" s="41"/>
-      <c r="Z43" s="41"/>
-      <c r="AA43" s="41"/>
-      <c r="AB43" s="41"/>
-      <c r="AC43" s="41"/>
+      <c r="I43" s="60"/>
+      <c r="J43" s="60"/>
+      <c r="K43" s="60"/>
+      <c r="L43" s="60"/>
+      <c r="M43" s="60"/>
+      <c r="N43" s="60"/>
+      <c r="O43" s="60"/>
+      <c r="P43" s="60"/>
+      <c r="Q43" s="60"/>
+      <c r="R43" s="60"/>
+      <c r="S43" s="60"/>
+      <c r="T43" s="60"/>
+      <c r="U43" s="60"/>
+      <c r="V43" s="60"/>
+      <c r="W43" s="60"/>
+      <c r="X43" s="60"/>
+      <c r="Y43" s="60"/>
+      <c r="Z43" s="60"/>
+      <c r="AA43" s="60"/>
+      <c r="AB43" s="60"/>
+      <c r="AC43" s="60"/>
     </row>
     <row r="44" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="6"/>
@@ -3620,35 +3594,69 @@
       <c r="AB47" s="41"/>
       <c r="AC47" s="41"/>
     </row>
-    <row r="48" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G48" s="3"/>
-    </row>
-    <row r="49" spans="3:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="9"/>
-      <c r="F49" s="8"/>
-    </row>
-    <row r="50" spans="3:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C50" s="4"/>
+    <row r="48" spans="1:29" s="37" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="6"/>
+      <c r="B48" s="61"/>
+      <c r="C48" s="62"/>
+      <c r="D48" s="63"/>
+      <c r="E48" s="64"/>
+      <c r="F48" s="64"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="I48" s="41"/>
+      <c r="J48" s="41"/>
+      <c r="K48" s="41"/>
+      <c r="L48" s="41"/>
+      <c r="M48" s="41"/>
+      <c r="N48" s="41"/>
+      <c r="O48" s="41"/>
+      <c r="P48" s="41"/>
+      <c r="Q48" s="41"/>
+      <c r="R48" s="41"/>
+      <c r="S48" s="41"/>
+      <c r="T48" s="41"/>
+      <c r="U48" s="41"/>
+      <c r="V48" s="41"/>
+      <c r="W48" s="41"/>
+      <c r="X48" s="41"/>
+      <c r="Y48" s="41"/>
+      <c r="Z48" s="41"/>
+      <c r="AA48" s="41"/>
+      <c r="AB48" s="41"/>
+      <c r="AC48" s="41"/>
+    </row>
+    <row r="49" spans="3:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G49" s="3"/>
+    </row>
+    <row r="50" spans="3:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C50" s="9"/>
+      <c r="F50" s="8"/>
+    </row>
+    <row r="51" spans="3:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C51" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="P6:V6"/>
+    <mergeCell ref="W6:AC6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="Q2:Z2"/>
+    <mergeCell ref="Q1:Z1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="I2:O2"/>
+    <mergeCell ref="I3:O3"/>
+    <mergeCell ref="Q3:Z3"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="E7:E8"/>
-    <mergeCell ref="Q1:Z1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="I2:O2"/>
-    <mergeCell ref="I3:O3"/>
-    <mergeCell ref="Q3:Z3"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="P6:V6"/>
-    <mergeCell ref="W6:AC6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="Q2:Z2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D9:D47">
+  <conditionalFormatting sqref="D9:D48">
     <cfRule type="dataBar" priority="23">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -3662,12 +3670,12 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6:AB47">
+  <conditionalFormatting sqref="I6:AB48">
     <cfRule type="expression" dxfId="13" priority="1">
       <formula>AND(TODAY()&gt;=I$7, TODAY()&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:AB17">
+  <conditionalFormatting sqref="I11:AB18">
     <cfRule type="expression" dxfId="12" priority="6">
       <formula>AND(task_start&lt;=I$7,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$7)</formula>
     </cfRule>
@@ -3675,7 +3683,7 @@
       <formula>AND(task_end&gt;=I$7,task_start&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I19:AB41">
+  <conditionalFormatting sqref="I20:AB42">
     <cfRule type="expression" dxfId="10" priority="4">
       <formula>AND(task_start&lt;=I$7,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$7)</formula>
     </cfRule>
@@ -3683,7 +3691,7 @@
       <formula>AND(task_end&gt;=I$7,task_start&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I43:AB47">
+  <conditionalFormatting sqref="I44:AB48">
     <cfRule type="expression" dxfId="8" priority="2">
       <formula>AND(task_start&lt;=I$7,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$7)</formula>
     </cfRule>
@@ -3691,12 +3699,12 @@
       <formula>AND(task_end&gt;=I$7,task_start&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC6:AC47">
+  <conditionalFormatting sqref="AC6:AC48">
     <cfRule type="expression" dxfId="6" priority="25">
       <formula>AND(TODAY()&gt;=AC$7, TODAY()&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC11:AC17">
+  <conditionalFormatting sqref="AC11:AC18">
     <cfRule type="expression" dxfId="5" priority="28">
       <formula>AND(task_start&lt;=AC$7,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=AC$7)</formula>
     </cfRule>
@@ -3704,7 +3712,7 @@
       <formula>AND(task_end&gt;=AC$7,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC19:AC41">
+  <conditionalFormatting sqref="AC20:AC42">
     <cfRule type="expression" dxfId="3" priority="32">
       <formula>AND(task_start&lt;=AC$7,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=AC$7)</formula>
     </cfRule>
@@ -3712,7 +3720,7 @@
       <formula>AND(task_end&gt;=AC$7,task_start&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC43:AC47">
+  <conditionalFormatting sqref="AC44:AC48">
     <cfRule type="expression" dxfId="1" priority="36">
       <formula>AND(task_start&lt;=AC$7,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=AC$7)</formula>
     </cfRule>
@@ -3721,10 +3729,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C43:C47 C19:C21 C22:C41" xr:uid="{81BFDE51-3151-43F8-A7A1-718D27BBADDF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C44:C48 C20:C42" xr:uid="{81BFDE51-3151-43F8-A7A1-718D27BBADDF}">
       <formula1>$B$2:$B$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C11:C17" xr:uid="{57E84E88-ADF7-4240-9B38-62294B230932}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C11:C18" xr:uid="{57E84E88-ADF7-4240-9B38-62294B230932}">
       <formula1>$B$2:$B$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -3734,7 +3742,6 @@
   <headerFooter differentFirst="1" scaleWithDoc="0">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -3751,7 +3758,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D9:D47</xm:sqref>
+          <xm:sqref>D9:D48</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -3760,6 +3767,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -4071,36 +4107,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A09426A3-87E9-4865-8A6C-3456B026AE03}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4121,33 +4155,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>